--- a/measurements/32/Filled_2D_sections/axial/week32_axial_Batch_Allmarks.xlsx
+++ b/measurements/32/Filled_2D_sections/axial/week32_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,107 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +601,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.38786436644854</v>
+        <v>3959.637188208616</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35842730650088</v>
+        <v>338.9026283650171</v>
       </c>
       <c r="E2" t="n">
-        <v>14.0121844221906</v>
+        <v>273.5712196713402</v>
       </c>
       <c r="F2" t="n">
         <v>1.238809509173385</v>
@@ -525,24 +620,57 @@
         <v>0.4332268693774552</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5113376524390244</v>
+        <v>1.655505952380952</v>
       </c>
       <c r="J2" t="n">
-        <v>0.743235518292683</v>
+        <v>14.51078869047619</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6272865853658537</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>5.959821428571427</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14.51078869047619</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.479166666666666</v>
+      </c>
+      <c r="U2" t="n">
+        <v>9.983258928571429</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7.009672619047619</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.655505952380952</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.524925595238095</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.509765625</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>10.10762938726948</v>
+      <c r="AH2" s="2" t="n">
+        <v>3852.81746031746</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +681,79 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.758774538964902</v>
+        <v>3719.841269841269</v>
       </c>
       <c r="D3" t="n">
-        <v>21.77048688400082</v>
+        <v>425.0428391638256</v>
       </c>
       <c r="E3" t="n">
-        <v>13.949116497505</v>
+        <v>272.3398935227167</v>
       </c>
       <c r="F3" t="n">
         <v>1.560707223851402</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2587431521623715</v>
+        <v>0.2587431521623716</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.907366071428571</v>
+      </c>
+      <c r="J3" t="n">
+        <v>37.18005952380952</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10.30443948412698</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>37.18005952380952</v>
+      </c>
+      <c r="N3" t="n">
+        <v>14.29129464285714</v>
+      </c>
+      <c r="P3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.5042873475609756</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.904344512195122</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.9126333841463414</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="T3" t="n">
+        <v>5.197172619047619</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9.955357142857142</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.789713541666666</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.040178571428571</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.162202380952381</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.907366071428571</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>19.61569761444883</v>
+      <c r="AH3" s="2" t="n">
+        <v>382.9731439011438</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +764,76 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.34622248661511</v>
+        <v>3943.764172335601</v>
       </c>
       <c r="D4" t="n">
-        <v>18.1793261388453</v>
+        <v>354.9297008060274</v>
       </c>
       <c r="E4" t="n">
-        <v>13.98952754532419</v>
+        <v>273.128871122996</v>
       </c>
       <c r="F4" t="n">
         <v>1.299495360364868</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3934015940459996</v>
+        <v>0.3934015940459995</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5246760670731707</v>
+        <v>1.551339285714286</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7086509146341463</v>
+        <v>13.83556547619048</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6397357723577236</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>7.451636904761906</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13.83556547619048</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13.39099702380952</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.538690476190476</v>
+      </c>
+      <c r="U4" t="n">
+        <v>10.24367559523809</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.966889880952381</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.452380952380952</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.551339285714286</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>13.34528205322056</v>
+      <c r="AH4" s="2" t="n">
+        <v>260.5507448485919</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +844,75 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.4797739440809</v>
+        <v>3994.671201814059</v>
       </c>
       <c r="D5" t="n">
-        <v>19.15595129350337</v>
+        <v>373.9971443017324</v>
       </c>
       <c r="E5" t="n">
-        <v>13.75399449104216</v>
+        <v>268.5303686346326</v>
       </c>
       <c r="F5" t="n">
         <v>1.39275548684998</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3588841931465931</v>
+        <v>0.3588841931465933</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5028582317073171</v>
+        <v>2.505580357142857</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6831173780487805</v>
+        <v>13.33705357142857</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6221735264227642</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>7.887369791666666</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13.33705357142857</v>
+      </c>
+      <c r="N5" t="n">
+        <v>13.28683035714286</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5.282738095238095</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9.817708333333332</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.529761904761904</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.850446428571428</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.505580357142857</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AH5" s="2" t="n">
         <v>1.469859301803325</v>
       </c>
     </row>
@@ -694,17 +924,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10.25044616299822</v>
+        <v>3907.256235827664</v>
       </c>
       <c r="D6" t="n">
-        <v>23.16246410986273</v>
+        <v>452.2195373830341</v>
       </c>
       <c r="E6" t="n">
-        <v>13.52091282169993</v>
+        <v>263.9797265189034</v>
       </c>
       <c r="F6" t="n">
         <v>1.713084346841502</v>
@@ -713,24 +943,60 @@
         <v>0.2400949990631174</v>
       </c>
       <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.940104166666667</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.56175595238095</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10.20624069940476</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>35.56175595238095</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13.46912202380952</v>
+      </c>
+      <c r="P6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.5178163109756098</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.821455792682927</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.009717987804878</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>10.10974702380952</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9.534970238095237</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.502232142857142</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.169642857142857</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.36235119047619</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.940104166666667</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.3365112300131731</v>
+      <c r="AH6" s="2" t="n">
+        <v>0.3365112300131732</v>
       </c>
     </row>
     <row r="7">
@@ -741,43 +1007,79 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.48364069006544</v>
+        <v>3996.145124716553</v>
       </c>
       <c r="D7" t="n">
-        <v>21.61129387704338</v>
+        <v>421.9347852184659</v>
       </c>
       <c r="E7" t="n">
-        <v>13.46621429047934</v>
+        <v>262.9118028141203</v>
       </c>
       <c r="F7" t="n">
         <v>1.604852960963397</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2820723090564812</v>
+        <v>0.2820723090564813</v>
       </c>
       <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.213541666666667</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.50334821428572</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.613792782738097</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>34.50334821428572</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13.28869047619048</v>
+      </c>
+      <c r="P7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.5161013719512195</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.767244664634146</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.9879954268292684</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="Q7" t="n">
+        <v>10.07626488095238</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.723586309523809</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.282738095238095</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.266369047619047</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.555803571428571</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.213541666666667</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>2.7</v>
+      <c r="AH7" s="2" t="n">
+        <v>11.2</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1090,79 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.63741820345033</v>
+        <v>4054.761904761905</v>
       </c>
       <c r="D8" t="n">
-        <v>19.80683648004765</v>
+        <v>386.7049027056921</v>
       </c>
       <c r="E8" t="n">
-        <v>13.4258032193998</v>
+        <v>262.1228247597104</v>
       </c>
       <c r="F8" t="n">
         <v>1.475281303946678</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3407343088373547</v>
+        <v>0.3407343088373549</v>
       </c>
       <c r="H8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.294642857142857</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.60305059523809</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.120453042328043</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.6790205792682927</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.465034298780488</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.07202743902439</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>28.60305059523809</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13.25706845238095</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.498883928571429</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.391369047619047</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.375744047619047</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.294642857142857</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.718377976190476</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.739490327380953</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6557450457317073</v>
+      <c r="AH8" s="2" t="n">
+        <v>1.815755208333333</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1173,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10.43783462224866</v>
+        <v>3978.684807256236</v>
       </c>
       <c r="D9" t="n">
-        <v>21.26289704369336</v>
+        <v>415.1327518054417</v>
       </c>
       <c r="E9" t="n">
-        <v>13.3711046678264</v>
+        <v>261.054900657563</v>
       </c>
       <c r="F9" t="n">
         <v>1.590212444814393</v>
@@ -854,24 +1192,63 @@
         <v>0.290118486387331</v>
       </c>
       <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.356026785714286</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.44791666666666</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.464657738095237</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.6898818597560976</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.405868902439025</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.9345782520325204</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>27.44791666666666</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13.82254464285714</v>
+      </c>
+      <c r="O9" t="n">
+        <v>13.46912202380952</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8.880208333333332</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5.600818452380952</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.537574404761904</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.356026785714286</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.645833333333333</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.472098214285714</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.271970274390244</v>
+      <c r="AH9" s="2" t="n">
+        <v>24.83370535714285</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1259,79 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.3167757287329</v>
+        <v>3932.539682539682</v>
       </c>
       <c r="D10" t="n">
-        <v>20.80121576495287</v>
+        <v>406.1189744586036</v>
       </c>
       <c r="E10" t="n">
-        <v>13.39131018882845</v>
+        <v>261.4493894009363</v>
       </c>
       <c r="F10" t="n">
         <v>1.55333686335681</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2996238747823686</v>
+        <v>0.2996238747823685</v>
       </c>
       <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.033110119047619</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26.46205357142857</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.815205627705627</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.7061737804878049</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.355373475609756</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.9352451727642276</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>26.46205357142857</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14.52938988095238</v>
+      </c>
+      <c r="O10" t="n">
+        <v>13.78720238095238</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.32626488095238</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5.904017857142857</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.033110119047619</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.993675595238095</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.159722222222222</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9064651613313008</v>
+      <c r="AH10" s="2" t="n">
+        <v>7.367027512521373</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1342,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.28911362284355</v>
+        <v>3921.995464852607</v>
       </c>
       <c r="D11" t="n">
-        <v>21.05450298728012</v>
+        <v>411.0641059421358</v>
       </c>
       <c r="E11" t="n">
-        <v>13.36518657788998</v>
+        <v>260.9393569968996</v>
       </c>
       <c r="F11" t="n">
         <v>1.575324284818484</v>
@@ -948,16 +1361,63 @@
         <v>0.2916740817906035</v>
       </c>
       <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.209821428571428</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26.43043154761905</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.87202380952381</v>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.7045541158536586</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.35375381097561</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.9328633130081302</v>
+      <c r="M11" t="n">
+        <v>26.43043154761905</v>
+      </c>
+      <c r="N11" t="n">
+        <v>14.453125</v>
+      </c>
+      <c r="O11" t="n">
+        <v>13.75558035714286</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6.973586309523809</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.790550595238095</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.635416666666666</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.209821428571428</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.910714285714286</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1428,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.24063057703748</v>
+        <v>3903.514739229025</v>
       </c>
       <c r="D12" t="n">
-        <v>21.19839310646057</v>
+        <v>413.873389221373</v>
       </c>
       <c r="E12" t="n">
-        <v>13.38539212796746</v>
+        <v>261.3338463079361</v>
       </c>
       <c r="F12" t="n">
         <v>1.583696084791465</v>
@@ -987,16 +1447,63 @@
         <v>0.2863720843741634</v>
       </c>
       <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.020089285714286</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.812161796536798</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.7062690548780488</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.317073170731707</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.9125063516260162</v>
+      <c r="M12" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="N12" t="n">
+        <v>13.94345238095238</v>
+      </c>
+      <c r="O12" t="n">
+        <v>13.7890625</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.956845238095238</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6.023065476190476</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.452008928571428</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.020089285714286</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.692336309523809</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.811011904761904</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>24.83370535714285</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1514,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.30011897679952</v>
+        <v>3926.190476190476</v>
       </c>
       <c r="D13" t="n">
-        <v>19.36984278225317</v>
+        <v>378.1731209868476</v>
       </c>
       <c r="E13" t="n">
-        <v>13.25333810143355</v>
+        <v>258.7556486470359</v>
       </c>
       <c r="F13" t="n">
         <v>1.461506726381487</v>
@@ -1026,16 +1533,60 @@
         <v>0.344984762921757</v>
       </c>
       <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.3671875</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26.00446428571428</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.803540426587301</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.7073170731707318</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.331935975609756</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.019626524390244</v>
+      <c r="M13" t="n">
+        <v>26.00446428571428</v>
+      </c>
+      <c r="N13" t="n">
+        <v>13.80952380952381</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.168526785714286</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7.533482142857142</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.735491071428571</v>
+      </c>
+      <c r="W13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.3671875</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.956473214285714</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.630208333333333</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>14.58274592731829</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1597,82 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.08536585365854</v>
+        <v>3844.331065759637</v>
       </c>
       <c r="D14" t="n">
-        <v>20.34054988477288</v>
+        <v>397.1250215598515</v>
       </c>
       <c r="E14" t="n">
-        <v>13.18536748537203</v>
+        <v>257.4286032858349</v>
       </c>
       <c r="F14" t="n">
         <v>1.542660825141118</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3063205565020528</v>
+        <v>0.3063205565020529</v>
       </c>
       <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25.80915178571428</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.792439331501831</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.7405678353658537</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.321932164634146</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.9373729674796749</v>
+      <c r="M14" t="n">
+        <v>25.80915178571428</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14.63541666666667</v>
+      </c>
+      <c r="O14" t="n">
+        <v>14.45870535714286</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.125744047619047</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6.05282738095238</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.834449404761904</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.833705357142857</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.34343998015873</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>13.57116284013605</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1683,82 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.976502082093992</v>
+        <v>3802.834467120181</v>
       </c>
       <c r="D15" t="n">
-        <v>19.34126786487858</v>
+        <v>377.6152297428676</v>
       </c>
       <c r="E15" t="n">
-        <v>13.04494412933908</v>
+        <v>254.6870044299534</v>
       </c>
       <c r="F15" t="n">
-        <v>1.48266390971952</v>
+        <v>1.482663909719521</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3351338395506918</v>
+        <v>0.3351338395506917</v>
       </c>
       <c r="H15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.482514880952381</v>
+      </c>
+      <c r="J15" t="n">
+        <v>26.15513392857143</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.404124149659864</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.6853086890243902</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.339653201219512</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.9524263211382115</v>
+      <c r="M15" t="n">
+        <v>26.15513392857143</v>
+      </c>
+      <c r="N15" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>13.37983630952381</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.983258928571428</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.3359375</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.040178571428571</v>
+      </c>
+      <c r="W15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.482514880952381</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.764880952380952</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.564174107142857</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1769,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.930398572278406</v>
+        <v>3785.260770975056</v>
       </c>
       <c r="D16" t="n">
-        <v>19.45311628899923</v>
+        <v>379.7989370709374</v>
       </c>
       <c r="E16" t="n">
-        <v>13.07351902345332</v>
+        <v>255.2448952198029</v>
       </c>
       <c r="F16" t="n">
         <v>1.48797858129102</v>
@@ -1143,16 +1788,63 @@
         <v>0.3297601545805807</v>
       </c>
       <c r="H16" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.482514880952381</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26.40252976190476</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.196304563492062</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.6330030487804879</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.352324695121951</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.9509336890243901</v>
+      <c r="M16" t="n">
+        <v>26.40252976190476</v>
+      </c>
+      <c r="N16" t="n">
+        <v>16.93638392857143</v>
+      </c>
+      <c r="O16" t="n">
+        <v>12.35863095238095</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.401785714285714</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.518229166666666</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.162946428571428</v>
+      </c>
+      <c r="W16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.482514880952381</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.662574404761905</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.573784722222222</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>7.645399305555554</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1855,76 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.916716240333136</v>
+        <v>3780.045351473922</v>
       </c>
       <c r="D17" t="n">
-        <v>18.03991811740689</v>
+        <v>352.2079251493726</v>
       </c>
       <c r="E17" t="n">
-        <v>13.03902601614231</v>
+        <v>254.5714603151594</v>
       </c>
       <c r="F17" t="n">
         <v>1.383532642321097</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3829205080792525</v>
+        <v>0.3829205080792524</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5737423780487805</v>
+        <v>1.188616071428571</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9319740853658537</v>
+        <v>18.19568452380952</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7579712906504065</v>
+        <v>5.460689484126984</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18.19568452380952</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14.99813988095238</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>11.2016369047619</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5.924479166666666</v>
+      </c>
+      <c r="W17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.188616071428571</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.904389880952381</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.871854707792208</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>5.840618799603174</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1935,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.795359904818561</v>
+        <v>3733.786848072562</v>
       </c>
       <c r="D18" t="n">
-        <v>17.5486465750671</v>
+        <v>342.6164331322624</v>
       </c>
       <c r="E18" t="n">
-        <v>13.1567925447371</v>
+        <v>256.8707115877242</v>
       </c>
       <c r="F18" t="n">
         <v>1.333808868339025</v>
@@ -1221,16 +1954,60 @@
         <v>0.3997081528708767</v>
       </c>
       <c r="H18" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.584821428571428</v>
+      </c>
+      <c r="J18" t="n">
+        <v>21.06956845238095</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.559098639455783</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.7121760670731707</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.079173018292683</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.8956745426829268</v>
+      <c r="M18" t="n">
+        <v>21.06956845238095</v>
+      </c>
+      <c r="N18" t="n">
+        <v>13.90438988095238</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.47172619047619</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.941220238095238</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.298549107142857</v>
+      </c>
+      <c r="W18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.584821428571428</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.820684523809524</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.707403273809523</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>4.998604910714285</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +2018,79 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.693634741225461</v>
+        <v>3695.01133786848</v>
       </c>
       <c r="D19" t="n">
-        <v>17.54027713508141</v>
+        <v>342.4530297801608</v>
       </c>
       <c r="E19" t="n">
-        <v>13.02820530461102</v>
+        <v>254.3601988043104</v>
       </c>
       <c r="F19" t="n">
         <v>1.346331035240399</v>
       </c>
       <c r="G19" t="n">
-        <v>0.395934744011089</v>
+        <v>0.3959347440110889</v>
       </c>
       <c r="H19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>22.41257440476191</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.521763392857143</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6955030487804879</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.14796112804878</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.9217320884146342</v>
+      <c r="M19" t="n">
+        <v>22.41257440476191</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13.57886904761905</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.259672619047619</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6.192336309523809</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.059058779761905</v>
+      </c>
+      <c r="W19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.820684523809524</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.634626116071428</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>4.5654296875</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2101,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.500594883997621</v>
+        <v>3621.428571428571</v>
       </c>
       <c r="D20" t="n">
-        <v>17.20126506177391</v>
+        <v>335.8342226346334</v>
       </c>
       <c r="E20" t="n">
-        <v>12.8045084011264</v>
+        <v>249.9927830696106</v>
       </c>
       <c r="F20" t="n">
         <v>1.343375670733344</v>
@@ -1299,16 +2120,57 @@
         <v>0.4034966073135722</v>
       </c>
       <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.544642857142857</v>
+      </c>
+      <c r="J20" t="n">
+        <v>23.40773809523809</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.100570436507938</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.7139862804878049</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.198932926829268</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.9564596036585367</v>
+      <c r="M20" t="n">
+        <v>23.40773809523809</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13.93973214285714</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.270461309523809</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5.364583333333333</v>
+      </c>
+      <c r="W20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.544642857142857</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.649553571428571</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.028041294642857</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>8.214983258928569</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2181,76 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.325401546698394</v>
+        <v>3554.648526077097</v>
       </c>
       <c r="D21" t="n">
-        <v>18.11727358655232</v>
+        <v>353.7181985945928</v>
       </c>
       <c r="E21" t="n">
-        <v>12.68919320804317</v>
+        <v>247.7413912046523</v>
       </c>
       <c r="F21" t="n">
         <v>1.427771907127122</v>
       </c>
       <c r="G21" t="n">
-        <v>0.357019321409751</v>
+        <v>0.3570193214097511</v>
       </c>
       <c r="H21" t="n">
+        <v>11</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.457217261904762</v>
+      </c>
+      <c r="J21" t="n">
+        <v>23.63095238095238</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.99421672077922</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>1.09032012195122</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.210365853658537</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.150342987804878</v>
+      <c r="M21" t="n">
+        <v>23.63095238095238</v>
+      </c>
+      <c r="N21" t="n">
+        <v>21.28720238095238</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.065848214285714</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.975818452380952</v>
+      </c>
+      <c r="W21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.457217261904762</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.645833333333333</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.996651785714286</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>6.277948288690476</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2260,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>5.55</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2282,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>3.555803571428571</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2299,90 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>2.427455357142857</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>2.353670634920635</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>1.679811507936508</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>3.762896825396825</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>2.730199126683502</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/32/Filled_2D_sections/axial/week32_axial_Batch_Allmarks.xlsx
+++ b/measurements/32/Filled_2D_sections/axial/week32_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2388,4 +2594,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week32_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3852.817460317459</v>
+      </c>
+      <c r="D10" t="n">
+        <v>135.851911361371</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3554.648526077097</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4054.761904761905</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>382.9731439011438</v>
+      </c>
+      <c r="D11" t="n">
+        <v>33.85498440597364</v>
+      </c>
+      <c r="E11" t="n">
+        <v>335.8342226346334</v>
+      </c>
+      <c r="F11" t="n">
+        <v>452.2195373830341</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.469859301803325</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1223466141194006</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.238809509173385</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.713084346841502</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3365112300131732</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.05383739644026576</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2400949990631174</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4332268693774552</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>12</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>12</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>13</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>13</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>11</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>15</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>11</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>14</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>14</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>12</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0161.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.353049533108718</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.5712405705774793</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.9880869341680844</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.523051619306313</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" t="n">
+        <v>18.88574825310559</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.905940163468223</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12.35863095238095</v>
+      </c>
+      <c r="F48" t="n">
+        <v>37.18005952380952</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>67</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.304887393390191</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.786075639217316</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.040178571428571</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11.2016369047619</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>111</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.755372560060061</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6495202073313594</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.188616071428571</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.040178571428571</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>